--- a/NOPL_Lab_Roster.xlsx
+++ b/NOPL_Lab_Roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacmota/Documents/Claude/Projects/NOPL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7ECAAD8-EB2E-8D43-A7CC-897C3775C290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3C4BFF-4A78-B642-89C3-FE077BB23B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14720" yWindow="2780" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14720" yWindow="2780" windowWidth="43560" windowHeight="23880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="156">
   <si>
     <t>Name</t>
   </si>
@@ -480,25 +480,31 @@
     <t>2021 UA Graduate Council Fellowship; 2021 &amp; 2022 NSCA-F Women's Scholarship ($2,000 ea); 2022 TTU Whitacre Graduate Recruitment Fellowship; 2023 NSCA Outstanding Podium Presentation (Doctoral Student)</t>
   </si>
   <si>
-    <t>Transitioned to PhD at TTU under Dr. Grant Tinsley</t>
-  </si>
-  <si>
-    <t>Transitioned to PhD at OU under Dr. Sam Moore</t>
-  </si>
-  <si>
     <t>Kornkanok Sophonsakulrat</t>
   </si>
   <si>
-    <t>Transitioned to MS in Animal Science</t>
-  </si>
-  <si>
     <t>Attending OT School</t>
   </si>
   <si>
     <t>Attending PA School</t>
   </si>
   <si>
-    <t>Completing to MS in Nutrition</t>
+    <t>PhD student at the University of Virginia</t>
+  </si>
+  <si>
+    <t>PhD Student at Texas Tech University (Dr. Tinsley)</t>
+  </si>
+  <si>
+    <t>Completing MS in Nutrition</t>
+  </si>
+  <si>
+    <t>Completing MS in Animal Science</t>
+  </si>
+  <si>
+    <t>Obtained Tenure and Promotion to Assocaite Professor effective 2026.09.01</t>
+  </si>
+  <si>
+    <t>PhD student at OU under Dr. Sam Moore</t>
   </si>
 </sst>
 </file>
@@ -594,7 +600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -617,6 +623,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -940,6 +947,9 @@
       <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="G2" s="12" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -1025,6 +1035,9 @@
       <c r="G6" t="s">
         <v>21</v>
       </c>
+      <c r="H6" t="s">
+        <v>150</v>
+      </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
@@ -1045,8 +1058,8 @@
       <c r="E7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>152</v>
+      <c r="H7" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -1110,8 +1123,8 @@
       <c r="E10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>152</v>
+      <c r="H10" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -1168,11 +1181,12 @@
       <c r="E13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>147</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" t="s">
         <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>151</v>
       </c>
       <c r="I13" t="s">
         <v>32</v>
@@ -1198,7 +1212,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>14</v>
@@ -1218,7 +1232,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>17</v>
@@ -1232,11 +1246,11 @@
       <c r="E16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="G16" t="s">
         <v>35</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="I16" t="s">
         <v>36</v>
@@ -1276,11 +1290,12 @@
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>153</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" t="s">
         <v>39</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1320,11 +1335,12 @@
       <c r="E20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" t="s">
         <v>43</v>
+      </c>
+      <c r="H20" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1348,7 +1364,7 @@
         <v>45</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
